--- a/output/details/2026-05-15/preprocessed_data.xlsx
+++ b/output/details/2026-05-15/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46157</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1097322838374562</v>
+        <v>-0.1109072682551184</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1757384177819606</v>
+        <v>-0.138727382796201</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1754903509297665</v>
+        <v>-0.1384539362551933</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1300492692345875</v>
+        <v>0.002281722403310785</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001702345719610122</v>
+        <v>0.001701429024439894</v>
       </c>
       <c r="G2" t="n">
-        <v>1.860677527051201</v>
+        <v>2.442655712753463</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4527130451921954</v>
+        <v>-0.2653397730052914</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
